--- a/testdata/configurationUAT/execute.xlsx
+++ b/testdata/configurationUAT/execute.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="283">
   <si>
     <t>App</t>
   </si>
@@ -774,46 +774,52 @@
     <t>C70896</t>
   </si>
   <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Model_97</t>
+  </si>
+  <si>
+    <t>C70897</t>
+  </si>
+  <si>
     <t>Cards-Transactions_Details_[MOB_ANDROID]-Debit_Cards</t>
   </si>
   <si>
-    <t>C70897</t>
+    <t>C70898</t>
   </si>
   <si>
     <t>Cards-Transactions_Details_[MOB_ANDROID]-Credit_Cards</t>
   </si>
   <si>
-    <t>C70898</t>
+    <t>C70899</t>
   </si>
   <si>
     <t>PAYMENTS-PAYMENTS_ARCHIVE-PAYMENTS_LIST_[ANDROID]</t>
   </si>
   <si>
-    <t>C70899</t>
+    <t>C70900</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts-Transactions_List_[MOB_ANDROID]</t>
   </si>
   <si>
-    <t>C70900</t>
+    <t>C70901</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions_List_[MOB_ANDROID]</t>
   </si>
   <si>
-    <t>C70901</t>
+    <t>C70902</t>
   </si>
   <si>
     <t>Payments_Upcoming_Payments_List_Of_Transactions_[MOB_ANDROID]</t>
   </si>
   <si>
-    <t>C70902</t>
+    <t>C70903</t>
   </si>
   <si>
     <t>Payments_Upcoming_Payments_Cancel_Payment_[MOB_ANDROID]</t>
   </si>
   <si>
-    <t>C70903</t>
+    <t>C70904</t>
   </si>
   <si>
     <t>Name</t>
@@ -1600,9 +1606,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1939,48 +1945,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
-    <col min="7" max="7" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+    <row r="1" customFormat="1" spans="1:7">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="11" t="s">
+    <row r="2" customFormat="1" spans="1:7">
+      <c r="A2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="14" t="s">
@@ -1989,21 +1994,21 @@
       <c r="F2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="G2" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:7">
+      <c r="A3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="14" t="s">
@@ -2012,21 +2017,21 @@
       <c r="F3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="G3" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:7">
+      <c r="A4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -2035,21 +2040,21 @@
       <c r="F4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="11" t="s">
+      <c r="G4" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:7">
+      <c r="A5" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="14" t="s">
@@ -2058,21 +2063,21 @@
       <c r="F5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="11" t="s">
+      <c r="G5" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:7">
+      <c r="A6" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -2081,21 +2086,21 @@
       <c r="F6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="11" t="s">
+      <c r="G6" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:7">
+      <c r="A7" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="14" t="s">
@@ -2104,21 +2109,21 @@
       <c r="F7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="11" t="s">
+      <c r="G7" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:7">
+      <c r="A8" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="14" t="s">
@@ -2127,21 +2132,21 @@
       <c r="F8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="11" t="s">
+      <c r="G8" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:7">
+      <c r="A9" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="14" t="s">
@@ -2150,21 +2155,21 @@
       <c r="F9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="11" t="s">
+      <c r="G9" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:7">
+      <c r="A10" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="14" t="s">
@@ -2173,21 +2178,21 @@
       <c r="F10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="11" t="s">
+      <c r="G10" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:7">
+      <c r="A11" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="14" t="s">
@@ -2196,21 +2201,21 @@
       <c r="F11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:7">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="14" t="s">
@@ -2219,21 +2224,21 @@
       <c r="F12" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="11" t="s">
+      <c r="G12" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:7">
+      <c r="A13" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="14" t="s">
@@ -2242,21 +2247,21 @@
       <c r="F13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="11" t="s">
+      <c r="G13" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:7">
+      <c r="A14" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="14" t="s">
@@ -2265,21 +2270,21 @@
       <c r="F14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="G14" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:7">
+      <c r="A15" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
@@ -2288,21 +2293,21 @@
       <c r="F15" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="G15" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:7">
+      <c r="A16" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="14" t="s">
@@ -2311,21 +2316,21 @@
       <c r="F16" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="G16" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:7">
+      <c r="A17" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="14" t="s">
@@ -2334,21 +2339,21 @@
       <c r="F17" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="11" t="s">
+      <c r="G17" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:7">
+      <c r="A18" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="14" t="s">
@@ -2357,21 +2362,21 @@
       <c r="F18" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="G18" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:7">
+      <c r="A19" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="14" t="s">
@@ -2380,21 +2385,21 @@
       <c r="F19" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="11" t="s">
+      <c r="G19" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:7">
+      <c r="A20" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="14" t="s">
@@ -2403,21 +2408,21 @@
       <c r="F20" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="G20" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:7">
+      <c r="A21" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="14" t="s">
@@ -2426,21 +2431,21 @@
       <c r="F21" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="11" t="s">
+      <c r="G21" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:7">
+      <c r="A22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="14" t="s">
@@ -2449,21 +2454,21 @@
       <c r="F22" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="11" t="s">
+      <c r="G22" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:7">
+      <c r="A23" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="14" t="s">
@@ -2472,21 +2477,21 @@
       <c r="F23" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="11" t="s">
+      <c r="G23" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:7">
+      <c r="A24" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="14" t="s">
@@ -2495,21 +2500,21 @@
       <c r="F24" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="11" t="s">
+      <c r="G24" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:7">
+      <c r="A25" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="14" t="s">
@@ -2518,21 +2523,21 @@
       <c r="F25" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="11" t="s">
+      <c r="G25" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:7">
+      <c r="A26" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="14" t="s">
@@ -2541,21 +2546,21 @@
       <c r="F26" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="11" t="s">
+      <c r="G26" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:7">
+      <c r="A27" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="14" t="s">
@@ -2564,21 +2569,21 @@
       <c r="F27" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="11" t="s">
+      <c r="G27" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:7">
+      <c r="A28" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="14" t="s">
@@ -2587,21 +2592,21 @@
       <c r="F28" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="G28" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:7">
+      <c r="A29" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="14" t="s">
@@ -2610,21 +2615,21 @@
       <c r="F29" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="G29" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:7">
+      <c r="A30" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="14" t="s">
@@ -2633,21 +2638,21 @@
       <c r="F30" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="11" t="s">
+      <c r="G30" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:7">
+      <c r="A31" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="14" t="s">
@@ -2656,21 +2661,21 @@
       <c r="F31" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="G31" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:7">
+      <c r="A32" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="14" t="s">
@@ -2679,21 +2684,21 @@
       <c r="F32" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="11" t="s">
+      <c r="G32" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:7">
+      <c r="A33" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="14" t="s">
@@ -2702,21 +2707,21 @@
       <c r="F33" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="11" t="s">
+      <c r="G33" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:7">
+      <c r="A34" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="14" t="s">
@@ -2725,21 +2730,21 @@
       <c r="F34" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="11" t="s">
+      <c r="G34" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:7">
+      <c r="A35" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="14" t="s">
@@ -2748,21 +2753,21 @@
       <c r="F35" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:7">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="14" t="s">
@@ -2771,21 +2776,21 @@
       <c r="F36" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="11" t="s">
+      <c r="G36" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:7">
+      <c r="A37" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="14" t="s">
@@ -2794,21 +2799,21 @@
       <c r="F37" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="11" t="s">
+      <c r="G37" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:7">
+      <c r="A38" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="14" t="s">
@@ -2817,21 +2822,21 @@
       <c r="F38" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="11" t="s">
+    <row r="39" customFormat="1" spans="1:7">
+      <c r="A39" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="14" t="s">
@@ -2840,21 +2845,21 @@
       <c r="F39" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="11" t="s">
+      <c r="G39" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:7">
+      <c r="A40" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="14" t="s">
@@ -2863,21 +2868,21 @@
       <c r="F40" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="11" t="s">
+      <c r="G40" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:7">
+      <c r="A41" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="14" t="s">
@@ -2886,21 +2891,21 @@
       <c r="F41" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="14" t="s">
@@ -2909,21 +2914,21 @@
       <c r="F42" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="11" t="s">
+      <c r="G42" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:7">
+      <c r="A43" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="14" t="s">
@@ -2932,21 +2937,21 @@
       <c r="F43" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="11" t="s">
+      <c r="G43" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:7">
+      <c r="A44" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="14" t="s">
@@ -2955,21 +2960,21 @@
       <c r="F44" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="11" t="s">
+      <c r="G44" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:7">
+      <c r="A45" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="14" t="s">
@@ -2978,21 +2983,21 @@
       <c r="F45" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="11" t="s">
+      <c r="G45" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:7">
+      <c r="A46" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="14" t="s">
@@ -3001,21 +3006,21 @@
       <c r="F46" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="11" t="s">
+      <c r="G46" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:7">
+      <c r="A47" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="14" t="s">
@@ -3024,21 +3029,21 @@
       <c r="F47" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="11" t="s">
+      <c r="G47" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:7">
+      <c r="A48" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="14" t="s">
@@ -3047,21 +3052,21 @@
       <c r="F48" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="11" t="s">
+      <c r="G48" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:7">
+      <c r="A49" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="14" t="s">
@@ -3070,21 +3075,21 @@
       <c r="F49" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="11" t="s">
+      <c r="G49" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:7">
+      <c r="A50" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="14" t="s">
@@ -3093,21 +3098,21 @@
       <c r="F50" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="11" t="s">
+      <c r="G50" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:7">
+      <c r="A51" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="14" t="s">
@@ -3116,21 +3121,21 @@
       <c r="F51" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="11" t="s">
+      <c r="G51" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:7">
+      <c r="A52" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="14" t="s">
@@ -3139,21 +3144,21 @@
       <c r="F52" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="11" t="s">
+      <c r="G52" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:7">
+      <c r="A53" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="14" t="s">
@@ -3162,21 +3167,21 @@
       <c r="F53" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="11" t="s">
+      <c r="G53" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:7">
+      <c r="A54" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="14" t="s">
@@ -3185,21 +3190,21 @@
       <c r="F54" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G54" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="11" t="s">
+      <c r="G54" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:7">
+      <c r="A55" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="14" t="s">
@@ -3208,21 +3213,21 @@
       <c r="F55" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" s="11" t="s">
+      <c r="G55" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:7">
+      <c r="A56" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="14" t="s">
@@ -3231,21 +3236,21 @@
       <c r="F56" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B57" s="11" t="s">
+      <c r="G56" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:7">
+      <c r="A57" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="14" t="s">
@@ -3254,21 +3259,21 @@
       <c r="F57" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="11" t="s">
+      <c r="G57" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:7">
+      <c r="A58" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="14" t="s">
@@ -3277,21 +3282,21 @@
       <c r="F58" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B59" s="11" t="s">
+      <c r="G58" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:7">
+      <c r="A59" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="14" t="s">
@@ -3300,21 +3305,21 @@
       <c r="F59" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G59" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60" s="11" t="s">
+      <c r="G59" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:7">
+      <c r="A60" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="14" t="s">
@@ -3323,21 +3328,21 @@
       <c r="F60" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B61" s="11" t="s">
+      <c r="G60" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:7">
+      <c r="A61" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="14" t="s">
@@ -3346,21 +3351,21 @@
       <c r="F61" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G61" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" s="11" t="s">
+      <c r="G61" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:7">
+      <c r="A62" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="14" t="s">
@@ -3369,21 +3374,21 @@
       <c r="F62" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" s="11" t="s">
+      <c r="G62" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:7">
+      <c r="A63" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="14" t="s">
@@ -3392,21 +3397,21 @@
       <c r="F63" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" s="11" t="s">
+      <c r="G63" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:7">
+      <c r="A64" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="14" t="s">
@@ -3415,21 +3420,21 @@
       <c r="F64" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G64" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B65" s="11" t="s">
+      <c r="G64" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:7">
+      <c r="A65" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="14" t="s">
@@ -3438,21 +3443,21 @@
       <c r="F65" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" s="11" t="s">
+      <c r="G65" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:7">
+      <c r="A66" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="14" t="s">
@@ -3461,21 +3466,21 @@
       <c r="F66" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" s="11" t="s">
+      <c r="G66" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:7">
+      <c r="A67" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="14" t="s">
@@ -3484,21 +3489,21 @@
       <c r="F67" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G67" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" s="11" t="s">
+      <c r="G67" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:7">
+      <c r="A68" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="14" t="s">
@@ -3507,21 +3512,21 @@
       <c r="F68" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B69" s="11" t="s">
+      <c r="G68" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:7">
+      <c r="A69" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="14" t="s">
@@ -3530,21 +3535,21 @@
       <c r="F69" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G69" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B70" s="11" t="s">
+      <c r="G69" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:7">
+      <c r="A70" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="14" t="s">
@@ -3553,21 +3558,21 @@
       <c r="F70" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" s="11" t="s">
+      <c r="G70" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:7">
+      <c r="A71" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D71" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="14" t="s">
@@ -3576,21 +3581,21 @@
       <c r="F71" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G71" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" s="11" t="s">
+      <c r="G71" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:7">
+      <c r="A72" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D72" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="14" t="s">
@@ -3599,21 +3604,21 @@
       <c r="F72" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B73" s="11" t="s">
+      <c r="G72" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="1:7">
+      <c r="A73" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="14" t="s">
@@ -3622,21 +3627,21 @@
       <c r="F73" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" s="11" t="s">
+      <c r="G73" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" spans="1:7">
+      <c r="A74" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="14" t="s">
@@ -3645,21 +3650,21 @@
       <c r="F74" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G74" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B75" s="11" t="s">
+      <c r="G74" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" spans="1:7">
+      <c r="A75" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="14" t="s">
@@ -3668,21 +3673,21 @@
       <c r="F75" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" s="11" t="s">
+      <c r="G75" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" spans="1:7">
+      <c r="A76" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="14" t="s">
@@ -3691,21 +3696,21 @@
       <c r="F76" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B77" s="11" t="s">
+      <c r="G76" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" spans="1:7">
+      <c r="A77" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="14" t="s">
@@ -3714,21 +3719,21 @@
       <c r="F77" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G77" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="11" t="s">
+      <c r="G77" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" spans="1:7">
+      <c r="A78" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D78" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E78" s="14" t="s">
@@ -3737,21 +3742,21 @@
       <c r="F78" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" s="11" t="s">
+      <c r="G78" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="1:7">
+      <c r="A79" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="14" t="s">
@@ -3760,21 +3765,21 @@
       <c r="F79" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G79" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" s="11" t="s">
+      <c r="G79" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" spans="1:7">
+      <c r="A80" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D80" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E80" s="14" t="s">
@@ -3783,21 +3788,21 @@
       <c r="F80" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B81" s="11" t="s">
+    <row r="81" customFormat="1" spans="1:7">
+      <c r="A81" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="14" t="s">
@@ -3806,21 +3811,21 @@
       <c r="F81" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B82" s="11" t="s">
+      <c r="G81" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="1:7">
+      <c r="A82" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="D82" s="11" t="s">
+      <c r="D82" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="14" t="s">
@@ -3829,21 +3834,21 @@
       <c r="F82" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" s="11" t="s">
+      <c r="G82" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" spans="1:7">
+      <c r="A83" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D83" s="11" t="s">
+      <c r="D83" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E83" s="14" t="s">
@@ -3852,21 +3857,21 @@
       <c r="F83" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B84" s="11" t="s">
+      <c r="G83" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" spans="1:7">
+      <c r="A84" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="D84" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E84" s="14" t="s">
@@ -3875,21 +3880,21 @@
       <c r="F84" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G84" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B85" s="11" t="s">
+      <c r="G84" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" spans="1:7">
+      <c r="A85" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="D85" s="11" t="s">
+      <c r="D85" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E85" s="14" t="s">
@@ -3898,21 +3903,21 @@
       <c r="F85" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B86" s="11" t="s">
+    <row r="86" customFormat="1" spans="1:7">
+      <c r="A86" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="D86" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E86" s="14" t="s">
@@ -3921,21 +3926,21 @@
       <c r="F86" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G86" s="11" t="s">
+      <c r="G86" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B87" s="11" t="s">
+    <row r="87" customFormat="1" spans="1:7">
+      <c r="A87" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D87" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="14" t="s">
@@ -3944,21 +3949,21 @@
       <c r="F87" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G87" s="11" t="s">
+      <c r="G87" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B88" s="11" t="s">
+    <row r="88" customFormat="1" spans="1:7">
+      <c r="A88" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="D88" s="11" t="s">
+      <c r="D88" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="14" t="s">
@@ -3967,21 +3972,21 @@
       <c r="F88" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="11" t="s">
+      <c r="G88" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B89" s="11" t="s">
+    <row r="89" customFormat="1" spans="1:7">
+      <c r="A89" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E89" s="14" t="s">
@@ -3990,21 +3995,21 @@
       <c r="F89" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B90" s="11" t="s">
+      <c r="G89" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" spans="1:7">
+      <c r="A90" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D90" s="11" t="s">
+      <c r="D90" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E90" s="14" t="s">
@@ -4013,21 +4018,21 @@
       <c r="F90" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G90" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B91" s="11" t="s">
+      <c r="G90" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:7">
+      <c r="A91" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="D91" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="14" t="s">
@@ -4036,21 +4041,21 @@
       <c r="F91" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B92" s="11" t="s">
+      <c r="G91" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" spans="1:7">
+      <c r="A92" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E92" s="14" t="s">
@@ -4059,21 +4064,21 @@
       <c r="F92" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B93" s="11" t="s">
+      <c r="G92" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" spans="1:7">
+      <c r="A93" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E93" s="14" t="s">
@@ -4082,21 +4087,21 @@
       <c r="F93" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G93" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B94" s="11" t="s">
+      <c r="G93" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" spans="1:7">
+      <c r="A94" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E94" s="14" t="s">
@@ -4105,21 +4110,21 @@
       <c r="F94" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G94" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B95" s="11" t="s">
+      <c r="G94" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:7">
+      <c r="A95" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="D95" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E95" s="14" t="s">
@@ -4128,21 +4133,21 @@
       <c r="F95" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G95" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B96" s="11" t="s">
+      <c r="G95" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" spans="1:7">
+      <c r="A96" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C96" s="11" t="s">
+      <c r="C96" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="D96" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E96" s="14" t="s">
@@ -4151,21 +4156,21 @@
       <c r="F96" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G96" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B97" s="11" t="s">
+      <c r="G96" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" spans="1:7">
+      <c r="A97" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D97" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E97" s="14" t="s">
@@ -4174,21 +4179,21 @@
       <c r="F97" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G97" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B98" s="11" t="s">
+      <c r="G97" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" customFormat="1" spans="1:7">
+      <c r="A98" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C98" s="11" t="s">
+      <c r="C98" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D98" s="11" t="s">
+      <c r="D98" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E98" s="14" t="s">
@@ -4197,21 +4202,21 @@
       <c r="F98" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G98" s="11" t="s">
+      <c r="G98" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B99" s="11" t="s">
+    <row r="99" customFormat="1" spans="1:7">
+      <c r="A99" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C99" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D99" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E99" s="14" t="s">
@@ -4220,21 +4225,21 @@
       <c r="F99" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B100" s="11" t="s">
+      <c r="G99" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" spans="1:7">
+      <c r="A100" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C100" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="D100" s="11" t="s">
+      <c r="D100" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E100" s="14" t="s">
@@ -4243,19 +4248,19 @@
       <c r="F100" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G100" s="11" t="s">
+      <c r="G100" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="11"/>
-      <c r="B101" s="11" t="s">
+    <row r="101" customFormat="1" spans="1:7">
+      <c r="A101" s="13"/>
+      <c r="B101" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C101" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D101" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E101" s="14" t="s">
@@ -4264,19 +4269,19 @@
       <c r="F101" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G101" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="11"/>
-      <c r="B102" s="11" t="s">
+      <c r="G101" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" spans="1:7">
+      <c r="A102" s="13"/>
+      <c r="B102" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C102" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="D102" s="11" t="s">
+      <c r="D102" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E102" s="14" t="s">
@@ -4285,19 +4290,19 @@
       <c r="F102" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="11"/>
-      <c r="B103" s="11" t="s">
+      <c r="G102" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" spans="1:7">
+      <c r="A103" s="13"/>
+      <c r="B103" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C103" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D103" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E103" s="14" t="s">
@@ -4306,19 +4311,19 @@
       <c r="F103" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G103" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="11"/>
-      <c r="B104" s="11" t="s">
+      <c r="G103" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" spans="1:7">
+      <c r="A104" s="13"/>
+      <c r="B104" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="D104" s="11" t="s">
+      <c r="D104" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E104" s="14" t="s">
@@ -4327,19 +4332,19 @@
       <c r="F104" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G104" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="11"/>
-      <c r="B105" s="11" t="s">
+      <c r="G104" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" customFormat="1" spans="1:7">
+      <c r="A105" s="13"/>
+      <c r="B105" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C105" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D105" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E105" s="14" t="s">
@@ -4348,19 +4353,19 @@
       <c r="F105" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G105" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106" s="11"/>
-      <c r="B106" s="11" t="s">
+      <c r="G105" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" spans="1:7">
+      <c r="A106" s="13"/>
+      <c r="B106" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C106" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D106" s="11" t="s">
+      <c r="D106" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E106" s="14" t="s">
@@ -4369,19 +4374,19 @@
       <c r="F106" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G106" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107" s="11"/>
-      <c r="B107" s="11" t="s">
+      <c r="G106" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" spans="1:7">
+      <c r="A107" s="13"/>
+      <c r="B107" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="D107" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E107" s="14" t="s">
@@ -4390,19 +4395,19 @@
       <c r="F107" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G107" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108" s="11"/>
-      <c r="B108" s="11" t="s">
+      <c r="G107" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" spans="1:7">
+      <c r="A108" s="13"/>
+      <c r="B108" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C108" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D108" s="11" t="s">
+      <c r="D108" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E108" s="14" t="s">
@@ -4411,19 +4416,19 @@
       <c r="F108" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G108" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" s="11"/>
-      <c r="B109" s="11" t="s">
+      <c r="G108" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" spans="1:7">
+      <c r="A109" s="13"/>
+      <c r="B109" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C109" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="D109" s="11" t="s">
+      <c r="D109" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E109" s="14" t="s">
@@ -4432,19 +4437,19 @@
       <c r="F109" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G109" s="11" t="s">
+      <c r="G109" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="11"/>
-      <c r="B110" s="11" t="s">
+    <row r="110" customFormat="1" spans="1:7">
+      <c r="A110" s="13"/>
+      <c r="B110" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C110" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D110" s="11" t="s">
+      <c r="D110" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E110" s="14" t="s">
@@ -4453,19 +4458,19 @@
       <c r="F110" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G110" s="11" t="s">
+      <c r="G110" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="11"/>
-      <c r="B111" s="11" t="s">
+    <row r="111" customFormat="1" spans="1:7">
+      <c r="A111" s="13"/>
+      <c r="B111" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="D111" s="11" t="s">
+      <c r="D111" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E111" s="14" t="s">
@@ -4474,19 +4479,19 @@
       <c r="F111" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G111" s="11" t="s">
+      <c r="G111" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
-      <c r="A112" s="11"/>
-      <c r="B112" s="11" t="s">
+    <row r="112" customFormat="1" spans="1:7">
+      <c r="A112" s="13"/>
+      <c r="B112" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D112" s="11" t="s">
+      <c r="D112" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E112" s="14" t="s">
@@ -4495,19 +4500,19 @@
       <c r="F112" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G112" s="11" t="s">
+      <c r="G112" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="11"/>
-      <c r="B113" s="11" t="s">
+    <row r="113" customFormat="1" spans="1:7">
+      <c r="A113" s="13"/>
+      <c r="B113" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C113" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D113" s="11" t="s">
+      <c r="D113" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E113" s="14" t="s">
@@ -4516,19 +4521,19 @@
       <c r="F113" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G113" s="11" t="s">
+      <c r="G113" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="11"/>
-      <c r="B114" s="11" t="s">
+    <row r="114" customFormat="1" spans="1:7">
+      <c r="A114" s="13"/>
+      <c r="B114" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C114" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="D114" s="11" t="s">
+      <c r="D114" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E114" s="14" t="s">
@@ -4537,19 +4542,19 @@
       <c r="F114" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G114" s="11" t="s">
+      <c r="G114" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="11"/>
-      <c r="B115" s="11" t="s">
+    <row r="115" customFormat="1" spans="1:7">
+      <c r="A115" s="13"/>
+      <c r="B115" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D115" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E115" s="14" t="s">
@@ -4558,19 +4563,19 @@
       <c r="F115" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="11" t="s">
+      <c r="G115" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="11"/>
-      <c r="B116" s="11" t="s">
+    <row r="116" customFormat="1" spans="1:7">
+      <c r="A116" s="13"/>
+      <c r="B116" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="D116" s="11" t="s">
+      <c r="D116" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E116" s="14" t="s">
@@ -4579,19 +4584,19 @@
       <c r="F116" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G116" s="11" t="s">
+      <c r="G116" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
-      <c r="A117" s="11"/>
-      <c r="B117" s="11" t="s">
+    <row r="117" customFormat="1" spans="1:7">
+      <c r="A117" s="13"/>
+      <c r="B117" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="D117" s="11" t="s">
+      <c r="D117" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E117" s="14" t="s">
@@ -4600,19 +4605,19 @@
       <c r="F117" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G117" s="11" t="s">
+      <c r="G117" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
-      <c r="A118" s="11"/>
-      <c r="B118" s="11" t="s">
+    <row r="118" customFormat="1" spans="1:7">
+      <c r="A118" s="13"/>
+      <c r="B118" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="D118" s="11" t="s">
+      <c r="D118" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E118" s="14" t="s">
@@ -4621,19 +4626,19 @@
       <c r="F118" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G118" s="11" t="s">
+      <c r="G118" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
-      <c r="A119" s="11"/>
-      <c r="B119" s="11" t="s">
+    <row r="119" customFormat="1" spans="1:7">
+      <c r="A119" s="13"/>
+      <c r="B119" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="D119" s="11" t="s">
+      <c r="D119" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E119" s="14" t="s">
@@ -4642,19 +4647,19 @@
       <c r="F119" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G119" s="11" t="s">
+      <c r="G119" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
-      <c r="A120" s="11"/>
-      <c r="B120" s="11" t="s">
+    <row r="120" customFormat="1" spans="1:7">
+      <c r="A120" s="13"/>
+      <c r="B120" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C120" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="D120" s="11" t="s">
+      <c r="D120" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E120" s="14" t="s">
@@ -4663,19 +4668,19 @@
       <c r="F120" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G120" s="11" t="s">
+      <c r="G120" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
-      <c r="A121" s="11"/>
-      <c r="B121" s="11" t="s">
+    <row r="121" customFormat="1" spans="1:7">
+      <c r="A121" s="13"/>
+      <c r="B121" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C121" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D121" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E121" s="14" t="s">
@@ -4684,19 +4689,19 @@
       <c r="F121" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G121" s="11" t="s">
+      <c r="G121" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
-      <c r="A122" s="11"/>
-      <c r="B122" s="11" t="s">
+    <row r="122" customFormat="1" spans="1:7">
+      <c r="A122" s="13"/>
+      <c r="B122" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C122" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D122" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E122" s="14" t="s">
@@ -4705,19 +4710,19 @@
       <c r="F122" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G122" s="11" t="s">
+      <c r="G122" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
-      <c r="A123" s="11"/>
-      <c r="B123" s="11" t="s">
+    <row r="123" customFormat="1" spans="1:7">
+      <c r="A123" s="13"/>
+      <c r="B123" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C123" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D123" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E123" s="14" t="s">
@@ -4726,19 +4731,19 @@
       <c r="F123" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G123" s="11" t="s">
+      <c r="G123" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
-      <c r="A124" s="11"/>
-      <c r="B124" s="11" t="s">
+    <row r="124" customFormat="1" spans="1:7">
+      <c r="A124" s="13"/>
+      <c r="B124" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C124" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="D124" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E124" s="14" t="s">
@@ -4747,19 +4752,19 @@
       <c r="F124" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G124" s="11" t="s">
+      <c r="G124" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
-      <c r="A125" s="11"/>
-      <c r="B125" s="11" t="s">
+    <row r="125" customFormat="1" spans="1:7">
+      <c r="A125" s="13"/>
+      <c r="B125" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="C125" s="11" t="s">
+      <c r="C125" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D125" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E125" s="14" t="s">
@@ -4768,305 +4773,326 @@
       <c r="F125" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G125" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126" s="11"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="11"/>
-      <c r="F126" s="15"/>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127" s="11"/>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
+      <c r="G125" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="126" customFormat="1" spans="1:7">
+      <c r="A126" s="13"/>
+      <c r="B126" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G126" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="127" customFormat="1" spans="1:7">
+      <c r="A127" s="13"/>
+      <c r="B127" s="13"/>
+      <c r="C127" s="13"/>
+      <c r="D127" s="13"/>
+      <c r="E127" s="13"/>
       <c r="F127" s="15"/>
     </row>
-    <row r="128" spans="1:7">
-      <c r="A128" s="11"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="11"/>
+    <row r="128" customFormat="1" spans="1:7">
+      <c r="A128" s="13"/>
+      <c r="B128" s="13"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
       <c r="F128" s="15"/>
     </row>
-    <row r="129" spans="1:6">
-      <c r="A129" s="11"/>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="11"/>
+    <row r="129" customFormat="1" spans="1:6">
+      <c r="A129" s="13"/>
+      <c r="B129" s="13"/>
+      <c r="C129" s="13"/>
+      <c r="D129" s="13"/>
+      <c r="E129" s="13"/>
       <c r="F129" s="15"/>
     </row>
-    <row r="130" spans="1:6">
-      <c r="A130" s="11"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="11"/>
+    <row r="130" customFormat="1" spans="1:6">
+      <c r="A130" s="13"/>
+      <c r="B130" s="13"/>
+      <c r="C130" s="13"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="13"/>
       <c r="F130" s="15"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="A131" s="11"/>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="11"/>
+    <row r="131" customFormat="1" spans="1:6">
+      <c r="A131" s="13"/>
+      <c r="B131" s="13"/>
+      <c r="C131" s="13"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="13"/>
       <c r="F131" s="15"/>
     </row>
-    <row r="132" spans="1:6">
-      <c r="A132" s="11"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="11"/>
+    <row r="132" customFormat="1" spans="1:6">
+      <c r="A132" s="13"/>
+      <c r="B132" s="13"/>
+      <c r="C132" s="13"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="13"/>
       <c r="F132" s="15"/>
     </row>
-    <row r="133" spans="1:6">
-      <c r="A133" s="11"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
+    <row r="133" customFormat="1" spans="1:6">
+      <c r="A133" s="13"/>
+      <c r="B133" s="13"/>
+      <c r="C133" s="13"/>
+      <c r="D133" s="13"/>
+      <c r="E133" s="13"/>
       <c r="F133" s="15"/>
     </row>
-    <row r="134" spans="1:6">
-      <c r="A134" s="11"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="11"/>
-      <c r="E134" s="11"/>
+    <row r="134" customFormat="1" spans="1:6">
+      <c r="A134" s="13"/>
+      <c r="B134" s="13"/>
+      <c r="C134" s="13"/>
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
       <c r="F134" s="15"/>
     </row>
-    <row r="135" spans="1:6">
-      <c r="A135" s="11"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
+    <row r="135" customFormat="1" spans="1:6">
+      <c r="A135" s="13"/>
+      <c r="B135" s="13"/>
+      <c r="C135" s="13"/>
+      <c r="D135" s="13"/>
+      <c r="E135" s="13"/>
       <c r="F135" s="15"/>
     </row>
-    <row r="136" spans="1:6">
-      <c r="A136" s="11"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
+    <row r="136" customFormat="1" spans="1:6">
+      <c r="A136" s="13"/>
+      <c r="B136" s="13"/>
+      <c r="C136" s="13"/>
+      <c r="D136" s="13"/>
+      <c r="E136" s="13"/>
       <c r="F136" s="15"/>
     </row>
-    <row r="137" spans="1:6">
-      <c r="A137" s="11"/>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="11"/>
+    <row r="137" customFormat="1" spans="1:6">
+      <c r="A137" s="13"/>
+      <c r="B137" s="13"/>
+      <c r="C137" s="13"/>
+      <c r="D137" s="13"/>
+      <c r="E137" s="13"/>
       <c r="F137" s="15"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="A138" s="11"/>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
+    <row r="138" customFormat="1" spans="1:6">
+      <c r="A138" s="13"/>
+      <c r="B138" s="13"/>
+      <c r="C138" s="13"/>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
       <c r="F138" s="15"/>
     </row>
-    <row r="139" spans="1:6">
-      <c r="A139" s="11"/>
-      <c r="B139" s="11"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
+    <row r="139" customFormat="1" spans="1:6">
+      <c r="A139" s="13"/>
+      <c r="B139" s="13"/>
+      <c r="C139" s="13"/>
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
       <c r="F139" s="15"/>
     </row>
-    <row r="140" spans="1:6">
-      <c r="A140" s="11"/>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
+    <row r="140" customFormat="1" spans="1:6">
+      <c r="A140" s="13"/>
+      <c r="B140" s="13"/>
+      <c r="C140" s="13"/>
+      <c r="D140" s="13"/>
+      <c r="E140" s="13"/>
       <c r="F140" s="15"/>
     </row>
-    <row r="141" spans="1:6">
-      <c r="A141" s="11"/>
-      <c r="B141" s="11"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
+    <row r="141" customFormat="1" spans="1:6">
+      <c r="A141" s="13"/>
+      <c r="B141" s="13"/>
+      <c r="C141" s="13"/>
+      <c r="D141" s="13"/>
+      <c r="E141" s="13"/>
       <c r="F141" s="15"/>
     </row>
-    <row r="142" spans="1:6">
-      <c r="A142" s="11"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
+    <row r="142" customFormat="1" spans="1:6">
+      <c r="A142" s="13"/>
+      <c r="B142" s="13"/>
+      <c r="C142" s="13"/>
+      <c r="D142" s="13"/>
+      <c r="E142" s="13"/>
       <c r="F142" s="15"/>
     </row>
-    <row r="143" spans="1:6">
-      <c r="A143" s="11"/>
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
+    <row r="143" customFormat="1" spans="1:6">
+      <c r="A143" s="13"/>
+      <c r="B143" s="13"/>
+      <c r="C143" s="13"/>
+      <c r="D143" s="13"/>
+      <c r="E143" s="13"/>
       <c r="F143" s="15"/>
     </row>
-    <row r="144" spans="1:6">
-      <c r="A144" s="11"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
+    <row r="144" customFormat="1" spans="1:6">
+      <c r="A144" s="13"/>
+      <c r="B144" s="13"/>
+      <c r="C144" s="13"/>
+      <c r="D144" s="13"/>
+      <c r="E144" s="13"/>
       <c r="F144" s="15"/>
     </row>
-    <row r="145" spans="1:6">
-      <c r="A145" s="11"/>
-      <c r="B145" s="11"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="11"/>
-      <c r="E145" s="11"/>
+    <row r="145" customFormat="1" spans="1:6">
+      <c r="A145" s="13"/>
+      <c r="B145" s="13"/>
+      <c r="C145" s="13"/>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
       <c r="F145" s="15"/>
     </row>
-    <row r="146" spans="1:6">
-      <c r="A146" s="11"/>
-      <c r="B146" s="11"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
+    <row r="146" customFormat="1" spans="1:6">
+      <c r="A146" s="13"/>
+      <c r="B146" s="13"/>
+      <c r="C146" s="13"/>
+      <c r="D146" s="13"/>
+      <c r="E146" s="13"/>
       <c r="F146" s="15"/>
     </row>
-    <row r="147" spans="1:6">
-      <c r="A147" s="11"/>
-      <c r="B147" s="11"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="11"/>
+    <row r="147" customFormat="1" spans="1:6">
+      <c r="A147" s="13"/>
+      <c r="B147" s="13"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
       <c r="F147" s="15"/>
     </row>
-    <row r="148" spans="1:6">
-      <c r="A148" s="11"/>
-      <c r="B148" s="11"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="11"/>
-      <c r="E148" s="11"/>
+    <row r="148" customFormat="1" spans="1:6">
+      <c r="A148" s="13"/>
+      <c r="B148" s="13"/>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
       <c r="F148" s="15"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="A149" s="11"/>
-      <c r="B149" s="11"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="11"/>
+    <row r="149" customFormat="1" spans="1:6">
+      <c r="A149" s="13"/>
+      <c r="B149" s="13"/>
+      <c r="C149" s="13"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
       <c r="F149" s="15"/>
     </row>
-    <row r="150" spans="1:6">
-      <c r="A150" s="11"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="11"/>
-      <c r="D150" s="11"/>
-      <c r="E150" s="11"/>
+    <row r="150" customFormat="1" spans="1:6">
+      <c r="A150" s="13"/>
+      <c r="B150" s="13"/>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
       <c r="F150" s="15"/>
     </row>
-    <row r="151" spans="1:6">
-      <c r="A151" s="11"/>
-      <c r="B151" s="11"/>
-      <c r="C151" s="11"/>
-      <c r="D151" s="11"/>
-      <c r="E151" s="11"/>
+    <row r="151" customFormat="1" spans="1:6">
+      <c r="A151" s="13"/>
+      <c r="B151" s="13"/>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
       <c r="F151" s="15"/>
     </row>
-    <row r="152" spans="1:6">
-      <c r="A152" s="11"/>
-      <c r="B152" s="11"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
+    <row r="152" customFormat="1" spans="1:6">
+      <c r="A152" s="13"/>
+      <c r="B152" s="13"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
       <c r="F152" s="15"/>
     </row>
-    <row r="153" spans="1:6">
-      <c r="A153" s="11"/>
-      <c r="B153" s="11"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11"/>
+    <row r="153" customFormat="1" spans="1:6">
+      <c r="A153" s="13"/>
+      <c r="B153" s="13"/>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="13"/>
       <c r="F153" s="15"/>
     </row>
-    <row r="154" spans="1:6">
-      <c r="A154" s="11"/>
-      <c r="B154" s="11"/>
-      <c r="C154" s="11"/>
-      <c r="D154" s="11"/>
-      <c r="E154" s="11"/>
+    <row r="154" customFormat="1" spans="1:6">
+      <c r="A154" s="13"/>
+      <c r="B154" s="13"/>
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
+      <c r="E154" s="13"/>
       <c r="F154" s="15"/>
     </row>
-    <row r="155" spans="1:6">
-      <c r="A155" s="11"/>
-      <c r="B155" s="11"/>
-      <c r="C155" s="11"/>
-      <c r="D155" s="11"/>
-      <c r="E155" s="11"/>
+    <row r="155" customFormat="1" spans="1:6">
+      <c r="A155" s="13"/>
+      <c r="B155" s="13"/>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="13"/>
       <c r="F155" s="15"/>
     </row>
-    <row r="156" spans="1:6">
-      <c r="A156" s="11"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="11"/>
+    <row r="156" customFormat="1" spans="1:6">
+      <c r="A156" s="13"/>
+      <c r="B156" s="13"/>
+      <c r="C156" s="13"/>
+      <c r="D156" s="13"/>
+      <c r="E156" s="13"/>
       <c r="F156" s="15"/>
     </row>
-    <row r="157" spans="1:6">
-      <c r="A157" s="11"/>
-      <c r="B157" s="11"/>
-      <c r="C157" s="11"/>
-      <c r="D157" s="11"/>
-      <c r="E157" s="11"/>
+    <row r="157" customFormat="1" spans="1:6">
+      <c r="A157" s="13"/>
+      <c r="B157" s="13"/>
+      <c r="C157" s="13"/>
+      <c r="D157" s="13"/>
+      <c r="E157" s="13"/>
       <c r="F157" s="15"/>
     </row>
-    <row r="158" spans="1:6">
-      <c r="A158" s="11"/>
-      <c r="B158" s="11"/>
-      <c r="C158" s="11"/>
-      <c r="D158" s="11"/>
-      <c r="E158" s="11"/>
+    <row r="158" customFormat="1" spans="1:6">
+      <c r="A158" s="13"/>
+      <c r="B158" s="13"/>
+      <c r="C158" s="13"/>
+      <c r="D158" s="13"/>
+      <c r="E158" s="13"/>
       <c r="F158" s="15"/>
     </row>
-    <row r="159" spans="1:6">
-      <c r="A159" s="11"/>
-      <c r="B159" s="11"/>
-      <c r="C159" s="11"/>
-      <c r="D159" s="11"/>
-      <c r="E159" s="11"/>
+    <row r="159" customFormat="1" spans="1:6">
+      <c r="A159" s="13"/>
+      <c r="B159" s="13"/>
+      <c r="C159" s="13"/>
+      <c r="D159" s="13"/>
+      <c r="E159" s="13"/>
       <c r="F159" s="15"/>
     </row>
-    <row r="160" spans="1:6">
-      <c r="A160" s="11"/>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="11"/>
+    <row r="160" customFormat="1" spans="1:6">
+      <c r="A160" s="13"/>
+      <c r="B160" s="13"/>
+      <c r="C160" s="13"/>
+      <c r="D160" s="13"/>
+      <c r="E160" s="13"/>
       <c r="F160" s="15"/>
     </row>
-    <row r="161" spans="1:6">
-      <c r="A161" s="11"/>
-      <c r="B161" s="11"/>
-      <c r="C161" s="11"/>
-      <c r="D161" s="11"/>
-      <c r="E161" s="11"/>
+    <row r="161" customFormat="1" spans="1:6">
+      <c r="A161" s="13"/>
+      <c r="B161" s="13"/>
+      <c r="C161" s="13"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="13"/>
       <c r="F161" s="15"/>
     </row>
-    <row r="162" spans="1:6">
-      <c r="A162" s="11"/>
-      <c r="B162" s="11"/>
-      <c r="C162" s="11"/>
-      <c r="D162" s="11"/>
-      <c r="E162" s="11"/>
+    <row r="162" customFormat="1" spans="1:6">
+      <c r="A162" s="13"/>
+      <c r="B162" s="13"/>
+      <c r="C162" s="13"/>
+      <c r="D162" s="13"/>
+      <c r="E162" s="13"/>
       <c r="F162" s="15"/>
+    </row>
+    <row r="163" customFormat="1" spans="1:6">
+      <c r="A163" s="13"/>
+      <c r="B163" s="13"/>
+      <c r="C163" s="13"/>
+      <c r="D163" s="13"/>
+      <c r="E163" s="13"/>
+      <c r="F163" s="15"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G125" etc:filterBottomFollowUsedRange="0">
@@ -5095,16 +5121,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -5112,24 +5138,24 @@
         <v>179</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
       <c r="A3" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
@@ -5137,10 +5163,10 @@
         <v>181</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -5148,21 +5174,21 @@
         <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="D6" s="5"/>
     </row>
@@ -5171,13 +5197,13 @@
         <v>185</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -5185,10 +5211,10 @@
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
@@ -5196,10 +5222,10 @@
         <v>66</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
@@ -5207,10 +5233,10 @@
         <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D10" s="7"/>
     </row>
@@ -5219,10 +5245,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
@@ -5230,10 +5256,10 @@
         <v>72</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
@@ -5241,21 +5267,21 @@
         <v>58</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:4">
@@ -5263,10 +5289,10 @@
         <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:4">
@@ -5274,13 +5300,13 @@
         <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:4">
@@ -5288,10 +5314,10 @@
         <v>191</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -5300,10 +5326,10 @@
         <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:4">
@@ -5311,24 +5337,24 @@
         <v>117</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:4">
@@ -5336,10 +5362,10 @@
         <v>80</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
@@ -5347,21 +5373,21 @@
         <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
       <c r="A23" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
@@ -5369,10 +5395,10 @@
         <v>171</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
@@ -5380,10 +5406,10 @@
         <v>113</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:4">
@@ -5391,10 +5417,10 @@
         <v>135</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:4">
@@ -5402,10 +5428,10 @@
         <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:4">
@@ -5413,10 +5439,10 @@
         <v>125</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:4">
@@ -5424,10 +5450,10 @@
         <v>175</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:4">
@@ -5435,10 +5461,10 @@
         <v>177</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:4">
@@ -5446,10 +5472,10 @@
         <v>207</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D31" s="7"/>
     </row>
@@ -5458,13 +5484,13 @@
         <v>193</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
@@ -5472,10 +5498,10 @@
         <v>195</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D33" s="7"/>
     </row>
@@ -5484,10 +5510,10 @@
         <v>197</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
@@ -5495,10 +5521,10 @@
         <v>199</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
@@ -5506,10 +5532,10 @@
         <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:4">
@@ -5517,10 +5543,10 @@
         <v>201</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:4">
@@ -5528,10 +5554,10 @@
         <v>18</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
@@ -5539,10 +5565,10 @@
         <v>203</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/configurationUAT/execute.xlsx
+++ b/testdata/configurationUAT/execute.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15936" windowHeight="8964"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$148</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="333">
   <si>
     <t>App</t>
   </si>
@@ -73,6 +73,9 @@
     <t>data</t>
   </si>
   <si>
+    <t>on</t>
+  </si>
+  <si>
     <t>Product_Summary-Loan_List_[MOB_ANDROID]</t>
   </si>
   <si>
@@ -871,15 +874,18 @@
     <t>C70913</t>
   </si>
   <si>
+    <t>5,</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Purpose_Code_289_invalid</t>
   </si>
   <si>
     <t>C70914</t>
   </si>
   <si>
-    <t>on</t>
-  </si>
-  <si>
     <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Without_Reference_Number_invalid</t>
   </si>
   <si>
@@ -932,6 +938,24 @@
   </si>
   <si>
     <t>C70923</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70924</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70925</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70926</t>
   </si>
   <si>
     <t>Name</t>
@@ -1020,6 +1044,9 @@
   </si>
   <si>
     <t>Automated Test Names</t>
+  </si>
+  <si>
+    <t>Formula-&gt;</t>
   </si>
 </sst>
 </file>
@@ -1735,7 +1762,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -1781,6 +1808,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1833,7 +1864,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1848,6 +1879,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2168,9 +2206,8 @@
       <c r="F2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B2,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G2" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="1" spans="1:7">
@@ -2178,10 +2215,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>10</v>
@@ -2192,9 +2229,8 @@
       <c r="F3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B3,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G3" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:7">
@@ -2202,10 +2238,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>10</v>
@@ -2216,9 +2252,8 @@
       <c r="F4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B4,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G4" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:7">
@@ -2226,10 +2261,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>10</v>
@@ -2240,9 +2275,8 @@
       <c r="F5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B5,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G5" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
@@ -2250,10 +2284,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>10</v>
@@ -2264,9 +2298,8 @@
       <c r="F6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B6,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G6" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -2274,10 +2307,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>10</v>
@@ -2288,9 +2321,8 @@
       <c r="F7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B7,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G7" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -2298,10 +2330,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>10</v>
@@ -2312,9 +2344,8 @@
       <c r="F8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B8,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G8" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:7">
@@ -2322,10 +2353,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>10</v>
@@ -2336,9 +2367,8 @@
       <c r="F9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B9,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G9" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:7">
@@ -2346,10 +2376,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>10</v>
@@ -2360,9 +2390,8 @@
       <c r="F10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B10,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G10" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:7">
@@ -2370,10 +2399,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>10</v>
@@ -2384,9 +2413,8 @@
       <c r="F11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B11,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G11" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:7">
@@ -2394,10 +2422,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>10</v>
@@ -2408,9 +2436,8 @@
       <c r="F12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B12,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G12" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:7">
@@ -2418,10 +2445,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>10</v>
@@ -2432,9 +2459,8 @@
       <c r="F13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B13,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G13" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:7">
@@ -2442,10 +2468,10 @@
         <v>7</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>10</v>
@@ -2456,9 +2482,8 @@
       <c r="F14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B14,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G14" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:7">
@@ -2466,10 +2491,10 @@
         <v>7</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>10</v>
@@ -2480,9 +2505,8 @@
       <c r="F15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B15,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G15" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:7">
@@ -2490,10 +2514,10 @@
         <v>7</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>10</v>
@@ -2504,9 +2528,8 @@
       <c r="F16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B16,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G16" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:7">
@@ -2514,10 +2537,10 @@
         <v>7</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>10</v>
@@ -2528,9 +2551,8 @@
       <c r="F17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B17,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G17" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:7">
@@ -2538,10 +2560,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>10</v>
@@ -2552,9 +2574,8 @@
       <c r="F18" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B18,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G18" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:7">
@@ -2562,10 +2583,10 @@
         <v>7</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>10</v>
@@ -2576,9 +2597,8 @@
       <c r="F19" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B19,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G19" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:7">
@@ -2586,10 +2606,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>10</v>
@@ -2600,9 +2620,8 @@
       <c r="F20" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B20,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G20" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:7">
@@ -2610,10 +2629,10 @@
         <v>7</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>10</v>
@@ -2624,9 +2643,8 @@
       <c r="F21" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B21,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G21" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:7">
@@ -2634,10 +2652,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>10</v>
@@ -2648,9 +2666,8 @@
       <c r="F22" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B22,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G22" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:7">
@@ -2658,10 +2675,10 @@
         <v>7</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>10</v>
@@ -2672,9 +2689,8 @@
       <c r="F23" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B23,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G23" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:7">
@@ -2682,10 +2698,10 @@
         <v>7</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>10</v>
@@ -2696,9 +2712,8 @@
       <c r="F24" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B24,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G24" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:7">
@@ -2706,10 +2721,10 @@
         <v>7</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>10</v>
@@ -2720,9 +2735,8 @@
       <c r="F25" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B25,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G25" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:7">
@@ -2730,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>10</v>
@@ -2744,9 +2758,8 @@
       <c r="F26" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B26,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G26" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:7">
@@ -2754,10 +2767,10 @@
         <v>7</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>10</v>
@@ -2768,9 +2781,8 @@
       <c r="F27" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B27,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G27" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:7">
@@ -2778,10 +2790,10 @@
         <v>7</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>10</v>
@@ -2792,9 +2804,8 @@
       <c r="F28" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B28,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G28" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:7">
@@ -2802,10 +2813,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>10</v>
@@ -2816,9 +2827,8 @@
       <c r="F29" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B29,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G29" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:7">
@@ -2826,10 +2836,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>10</v>
@@ -2840,9 +2850,8 @@
       <c r="F30" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B30,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G30" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:7">
@@ -2850,10 +2859,10 @@
         <v>7</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>10</v>
@@ -2864,9 +2873,8 @@
       <c r="F31" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B31,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G31" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:7">
@@ -2874,10 +2882,10 @@
         <v>7</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>10</v>
@@ -2888,9 +2896,8 @@
       <c r="F32" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B32,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G32" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:7">
@@ -2898,10 +2905,10 @@
         <v>7</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>10</v>
@@ -2912,9 +2919,8 @@
       <c r="F33" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B33,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G33" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:7">
@@ -2922,10 +2928,10 @@
         <v>7</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>10</v>
@@ -2936,9 +2942,8 @@
       <c r="F34" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B34,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G34" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:7">
@@ -2946,10 +2951,10 @@
         <v>7</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>10</v>
@@ -2960,9 +2965,8 @@
       <c r="F35" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B35,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G35" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:7">
@@ -2970,10 +2974,10 @@
         <v>7</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>10</v>
@@ -2984,9 +2988,8 @@
       <c r="F36" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B36,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G36" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:7">
@@ -2994,10 +2997,10 @@
         <v>7</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>10</v>
@@ -3008,9 +3011,8 @@
       <c r="F37" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B37,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G37" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:7">
@@ -3018,10 +3020,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>10</v>
@@ -3032,9 +3034,8 @@
       <c r="F38" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B38,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G38" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:7">
@@ -3042,10 +3043,10 @@
         <v>7</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>10</v>
@@ -3056,9 +3057,8 @@
       <c r="F39" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B39,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G39" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:7">
@@ -3066,10 +3066,10 @@
         <v>7</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>10</v>
@@ -3080,9 +3080,8 @@
       <c r="F40" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B40,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G40" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:7">
@@ -3090,10 +3089,10 @@
         <v>7</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>10</v>
@@ -3104,9 +3103,8 @@
       <c r="F41" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B41,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G41" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
@@ -3114,10 +3112,10 @@
         <v>7</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>10</v>
@@ -3128,9 +3126,8 @@
       <c r="F42" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B42,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G42" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:7">
@@ -3138,10 +3135,10 @@
         <v>7</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D43" s="15" t="s">
         <v>10</v>
@@ -3152,9 +3149,8 @@
       <c r="F43" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B43,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G43" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:7">
@@ -3162,10 +3158,10 @@
         <v>7</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>10</v>
@@ -3176,9 +3172,8 @@
       <c r="F44" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B44,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G44" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:7">
@@ -3186,10 +3181,10 @@
         <v>7</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>10</v>
@@ -3200,9 +3195,8 @@
       <c r="F45" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B45,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G45" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:7">
@@ -3210,10 +3204,10 @@
         <v>7</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>10</v>
@@ -3224,9 +3218,8 @@
       <c r="F46" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B46,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G46" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:7">
@@ -3234,10 +3227,10 @@
         <v>7</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>10</v>
@@ -3248,9 +3241,8 @@
       <c r="F47" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B47,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G47" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:7">
@@ -3258,10 +3250,10 @@
         <v>7</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>10</v>
@@ -3272,9 +3264,8 @@
       <c r="F48" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B48,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G48" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:7">
@@ -3282,10 +3273,10 @@
         <v>7</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>10</v>
@@ -3296,9 +3287,8 @@
       <c r="F49" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B49,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G49" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:7">
@@ -3306,10 +3296,10 @@
         <v>7</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>10</v>
@@ -3320,9 +3310,8 @@
       <c r="F50" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B50,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G50" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:7">
@@ -3330,10 +3319,10 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>10</v>
@@ -3344,9 +3333,8 @@
       <c r="F51" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G51" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B51,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G51" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:7">
@@ -3354,10 +3342,10 @@
         <v>7</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>10</v>
@@ -3368,9 +3356,8 @@
       <c r="F52" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B52,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G52" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:7">
@@ -3378,10 +3365,10 @@
         <v>7</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>10</v>
@@ -3392,9 +3379,8 @@
       <c r="F53" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B53,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G53" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -3402,10 +3388,10 @@
         <v>7</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>10</v>
@@ -3416,9 +3402,8 @@
       <c r="F54" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G54" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B54,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G54" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -3426,10 +3411,10 @@
         <v>7</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>10</v>
@@ -3440,9 +3425,8 @@
       <c r="F55" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B55,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G55" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:7">
@@ -3450,10 +3434,10 @@
         <v>7</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>10</v>
@@ -3464,9 +3448,8 @@
       <c r="F56" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G56" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B56,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G56" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:7">
@@ -3474,10 +3457,10 @@
         <v>7</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D57" s="15" t="s">
         <v>10</v>
@@ -3488,9 +3471,8 @@
       <c r="F57" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B57,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G57" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:7">
@@ -3498,10 +3480,10 @@
         <v>7</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D58" s="15" t="s">
         <v>10</v>
@@ -3512,9 +3494,8 @@
       <c r="F58" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B58,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G58" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:7">
@@ -3522,10 +3503,10 @@
         <v>7</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D59" s="15" t="s">
         <v>10</v>
@@ -3536,9 +3517,8 @@
       <c r="F59" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G59" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B59,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G59" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -3546,10 +3526,10 @@
         <v>7</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>10</v>
@@ -3560,9 +3540,8 @@
       <c r="F60" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B60,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G60" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:7">
@@ -3570,10 +3549,10 @@
         <v>7</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D61" s="15" t="s">
         <v>10</v>
@@ -3584,9 +3563,8 @@
       <c r="F61" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G61" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B61,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G61" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:7">
@@ -3594,10 +3572,10 @@
         <v>7</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>10</v>
@@ -3608,9 +3586,8 @@
       <c r="F62" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B62,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G62" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:7">
@@ -3618,10 +3595,10 @@
         <v>7</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>10</v>
@@ -3632,9 +3609,8 @@
       <c r="F63" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B63,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G63" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:7">
@@ -3642,10 +3618,10 @@
         <v>7</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>10</v>
@@ -3656,9 +3632,8 @@
       <c r="F64" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G64" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B64,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G64" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:7">
@@ -3666,10 +3641,10 @@
         <v>7</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D65" s="15" t="s">
         <v>10</v>
@@ -3680,9 +3655,8 @@
       <c r="F65" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B65,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G65" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:7">
@@ -3690,10 +3664,10 @@
         <v>7</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>10</v>
@@ -3704,9 +3678,8 @@
       <c r="F66" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B66,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G66" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:7">
@@ -3714,10 +3687,10 @@
         <v>7</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D67" s="15" t="s">
         <v>10</v>
@@ -3728,9 +3701,8 @@
       <c r="F67" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G67" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B67,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G67" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:7">
@@ -3738,10 +3710,10 @@
         <v>7</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>10</v>
@@ -3752,9 +3724,8 @@
       <c r="F68" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B68,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G68" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:7">
@@ -3762,10 +3733,10 @@
         <v>7</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D69" s="15" t="s">
         <v>10</v>
@@ -3776,9 +3747,8 @@
       <c r="F69" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G69" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B69,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G69" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -3786,10 +3756,10 @@
         <v>7</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D70" s="15" t="s">
         <v>10</v>
@@ -3800,9 +3770,8 @@
       <c r="F70" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B70,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G70" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:7">
@@ -3810,10 +3779,10 @@
         <v>7</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D71" s="15" t="s">
         <v>10</v>
@@ -3824,9 +3793,8 @@
       <c r="F71" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G71" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B71,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G71" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:7">
@@ -3834,10 +3802,10 @@
         <v>7</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D72" s="15" t="s">
         <v>10</v>
@@ -3848,9 +3816,8 @@
       <c r="F72" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B72,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G72" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:7">
@@ -3858,10 +3825,10 @@
         <v>7</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D73" s="15" t="s">
         <v>10</v>
@@ -3872,9 +3839,8 @@
       <c r="F73" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B73,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G73" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:7">
@@ -3882,10 +3848,10 @@
         <v>7</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>10</v>
@@ -3896,9 +3862,8 @@
       <c r="F74" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G74" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B74,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G74" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:7">
@@ -3906,10 +3871,10 @@
         <v>7</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D75" s="15" t="s">
         <v>10</v>
@@ -3920,9 +3885,8 @@
       <c r="F75" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B75,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G75" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:7">
@@ -3930,10 +3894,10 @@
         <v>7</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>10</v>
@@ -3944,9 +3908,8 @@
       <c r="F76" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B76,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G76" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:7">
@@ -3954,10 +3917,10 @@
         <v>7</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D77" s="15" t="s">
         <v>10</v>
@@ -3968,9 +3931,8 @@
       <c r="F77" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G77" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B77,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G77" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:7">
@@ -3978,10 +3940,10 @@
         <v>7</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>10</v>
@@ -3992,9 +3954,8 @@
       <c r="F78" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B78,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G78" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:7">
@@ -4002,10 +3963,10 @@
         <v>7</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>10</v>
@@ -4016,9 +3977,8 @@
       <c r="F79" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G79" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B79,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G79" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:7">
@@ -4026,10 +3986,10 @@
         <v>7</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>10</v>
@@ -4040,9 +4000,8 @@
       <c r="F80" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B80,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G80" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:7">
@@ -4050,10 +4009,10 @@
         <v>7</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D81" s="15" t="s">
         <v>10</v>
@@ -4064,9 +4023,8 @@
       <c r="F81" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G81" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B81,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G81" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:7">
@@ -4074,10 +4032,10 @@
         <v>7</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>10</v>
@@ -4088,9 +4046,8 @@
       <c r="F82" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B82,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G82" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -4098,10 +4055,10 @@
         <v>7</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D83" s="15" t="s">
         <v>10</v>
@@ -4112,9 +4069,8 @@
       <c r="F83" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G83" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B83,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G83" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -4122,10 +4078,10 @@
         <v>7</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>10</v>
@@ -4136,9 +4092,8 @@
       <c r="F84" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G84" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B84,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G84" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:7">
@@ -4146,10 +4101,10 @@
         <v>7</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D85" s="15" t="s">
         <v>10</v>
@@ -4160,9 +4115,8 @@
       <c r="F85" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G85" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B85,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G85" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:7">
@@ -4170,10 +4124,10 @@
         <v>7</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>10</v>
@@ -4184,9 +4138,8 @@
       <c r="F86" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G86" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B86,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G86" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:7">
@@ -4194,10 +4147,10 @@
         <v>7</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D87" s="15" t="s">
         <v>10</v>
@@ -4208,9 +4161,8 @@
       <c r="F87" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G87" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B87,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G87" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:7">
@@ -4218,10 +4170,10 @@
         <v>7</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>10</v>
@@ -4232,9 +4184,8 @@
       <c r="F88" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B88,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G88" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:7">
@@ -4242,10 +4193,10 @@
         <v>7</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D89" s="15" t="s">
         <v>10</v>
@@ -4256,9 +4207,8 @@
       <c r="F89" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B89,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G89" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:7">
@@ -4266,10 +4216,10 @@
         <v>7</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>10</v>
@@ -4280,9 +4230,8 @@
       <c r="F90" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G90" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B90,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G90" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:7">
@@ -4290,10 +4239,10 @@
         <v>7</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D91" s="15" t="s">
         <v>10</v>
@@ -4304,9 +4253,8 @@
       <c r="F91" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G91" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B91,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G91" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:7">
@@ -4314,10 +4262,10 @@
         <v>7</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>10</v>
@@ -4328,9 +4276,8 @@
       <c r="F92" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G92" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B92,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G92" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:7">
@@ -4338,10 +4285,10 @@
         <v>7</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D93" s="15" t="s">
         <v>10</v>
@@ -4352,9 +4299,8 @@
       <c r="F93" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G93" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B93,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G93" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -4362,10 +4308,10 @@
         <v>7</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>10</v>
@@ -4376,9 +4322,8 @@
       <c r="F94" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G94" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B94,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G94" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:7">
@@ -4386,10 +4331,10 @@
         <v>7</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D95" s="15" t="s">
         <v>10</v>
@@ -4400,9 +4345,8 @@
       <c r="F95" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G95" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B95,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G95" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:7">
@@ -4410,10 +4354,10 @@
         <v>7</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>10</v>
@@ -4424,9 +4368,8 @@
       <c r="F96" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G96" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B96,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G96" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:7">
@@ -4434,10 +4377,10 @@
         <v>7</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D97" s="15" t="s">
         <v>10</v>
@@ -4448,9 +4391,8 @@
       <c r="F97" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G97" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B97,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G97" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:7">
@@ -4458,10 +4400,10 @@
         <v>7</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>10</v>
@@ -4472,9 +4414,8 @@
       <c r="F98" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G98" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B98,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G98" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:7">
@@ -4482,10 +4423,10 @@
         <v>7</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D99" s="15" t="s">
         <v>10</v>
@@ -4496,9 +4437,8 @@
       <c r="F99" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B99,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G99" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:7">
@@ -4506,10 +4446,10 @@
         <v>7</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>10</v>
@@ -4520,9 +4460,8 @@
       <c r="F100" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G100" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B100,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G100" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:7">
@@ -4530,10 +4469,10 @@
         <v>7</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D101" s="15" t="s">
         <v>10</v>
@@ -4544,9 +4483,8 @@
       <c r="F101" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G101" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B101,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G101" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:7">
@@ -4554,10 +4492,10 @@
         <v>7</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>10</v>
@@ -4568,9 +4506,8 @@
       <c r="F102" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B102,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G102" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:7">
@@ -4578,10 +4515,10 @@
         <v>7</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D103" s="15" t="s">
         <v>10</v>
@@ -4592,9 +4529,8 @@
       <c r="F103" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G103" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B103,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G103" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:7">
@@ -4602,10 +4538,10 @@
         <v>7</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>10</v>
@@ -4616,9 +4552,8 @@
       <c r="F104" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G104" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B104,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G104" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -4626,10 +4561,10 @@
         <v>7</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>10</v>
@@ -4640,9 +4575,8 @@
       <c r="F105" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G105" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B105,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G105" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:7">
@@ -4650,10 +4584,10 @@
         <v>7</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>10</v>
@@ -4664,9 +4598,8 @@
       <c r="F106" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G106" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B106,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G106" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:7">
@@ -4674,10 +4607,10 @@
         <v>7</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D107" s="15" t="s">
         <v>10</v>
@@ -4688,9 +4621,8 @@
       <c r="F107" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G107" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B107,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G107" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:7">
@@ -4698,10 +4630,10 @@
         <v>7</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>10</v>
@@ -4712,9 +4644,8 @@
       <c r="F108" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G108" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B108,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G108" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:7">
@@ -4722,10 +4653,10 @@
         <v>7</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D109" s="15" t="s">
         <v>10</v>
@@ -4736,9 +4667,8 @@
       <c r="F109" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G109" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B109,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G109" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:7">
@@ -4746,10 +4676,10 @@
         <v>7</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>10</v>
@@ -4760,9 +4690,8 @@
       <c r="F110" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G110" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B110,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G110" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:7">
@@ -4770,10 +4699,10 @@
         <v>7</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D111" s="15" t="s">
         <v>10</v>
@@ -4784,9 +4713,8 @@
       <c r="F111" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G111" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B111,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G111" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:7">
@@ -4794,10 +4722,10 @@
         <v>7</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>10</v>
@@ -4808,9 +4736,8 @@
       <c r="F112" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G112" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B112,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G112" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:7">
@@ -4818,10 +4745,10 @@
         <v>7</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D113" s="15" t="s">
         <v>10</v>
@@ -4832,9 +4759,8 @@
       <c r="F113" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G113" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B113,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G113" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:7">
@@ -4842,10 +4768,10 @@
         <v>7</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>10</v>
@@ -4856,9 +4782,8 @@
       <c r="F114" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G114" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B114,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G114" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:7">
@@ -4866,10 +4791,10 @@
         <v>7</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D115" s="15" t="s">
         <v>10</v>
@@ -4880,9 +4805,8 @@
       <c r="F115" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B115,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G115" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:7">
@@ -4890,10 +4814,10 @@
         <v>7</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>10</v>
@@ -4904,9 +4828,8 @@
       <c r="F116" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G116" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B116,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G116" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:7">
@@ -4914,10 +4837,10 @@
         <v>7</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D117" s="15" t="s">
         <v>10</v>
@@ -4928,9 +4851,8 @@
       <c r="F117" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G117" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B117,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G117" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:7">
@@ -4938,10 +4860,10 @@
         <v>7</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D118" s="15" t="s">
         <v>10</v>
@@ -4952,9 +4874,8 @@
       <c r="F118" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G118" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B118,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G118" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:7">
@@ -4962,10 +4883,10 @@
         <v>7</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D119" s="15" t="s">
         <v>10</v>
@@ -4976,9 +4897,8 @@
       <c r="F119" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G119" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B119,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G119" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="120" customFormat="1" spans="1:7">
@@ -4986,10 +4906,10 @@
         <v>7</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>10</v>
@@ -5000,9 +4920,8 @@
       <c r="F120" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G120" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B120,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G120" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:7">
@@ -5010,10 +4929,10 @@
         <v>7</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>10</v>
@@ -5024,9 +4943,8 @@
       <c r="F121" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G121" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B121,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G121" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:7">
@@ -5034,10 +4952,10 @@
         <v>7</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>10</v>
@@ -5048,9 +4966,8 @@
       <c r="F122" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G122" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B122,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G122" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:7">
@@ -5058,10 +4975,10 @@
         <v>7</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D123" s="15" t="s">
         <v>10</v>
@@ -5072,9 +4989,8 @@
       <c r="F123" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G123" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B123,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G123" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="124" customFormat="1" spans="1:7">
@@ -5082,10 +4998,10 @@
         <v>7</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>10</v>
@@ -5096,9 +5012,8 @@
       <c r="F124" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G124" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B124,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G124" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="125" customFormat="1" spans="1:7">
@@ -5106,10 +5021,10 @@
         <v>7</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D125" s="15" t="s">
         <v>10</v>
@@ -5120,9 +5035,8 @@
       <c r="F125" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G125" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B125,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G125" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="126" customFormat="1" spans="1:7">
@@ -5130,10 +5044,10 @@
         <v>7</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>10</v>
@@ -5144,9 +5058,8 @@
       <c r="F126" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G126" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B126,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G126" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -5154,10 +5067,10 @@
         <v>7</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D127" s="15" t="s">
         <v>10</v>
@@ -5168,9 +5081,8 @@
       <c r="F127" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G127" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B127,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G127" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="128" customFormat="1" spans="1:7">
@@ -5178,10 +5090,10 @@
         <v>7</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>10</v>
@@ -5192,9 +5104,8 @@
       <c r="F128" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B128,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G128" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="129" customFormat="1" spans="1:7">
@@ -5202,10 +5113,10 @@
         <v>7</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D129" s="15" t="s">
         <v>10</v>
@@ -5216,9 +5127,8 @@
       <c r="F129" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G129" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B129,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G129" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="130" customFormat="1" spans="1:7">
@@ -5226,10 +5136,10 @@
         <v>7</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>10</v>
@@ -5240,9 +5150,8 @@
       <c r="F130" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G130" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B130,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G130" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="131" customFormat="1" spans="1:7">
@@ -5250,10 +5159,10 @@
         <v>7</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D131" s="15" t="s">
         <v>10</v>
@@ -5264,9 +5173,8 @@
       <c r="F131" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G131" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B131,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G131" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="132" customFormat="1" spans="1:7">
@@ -5274,10 +5182,10 @@
         <v>7</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D132" s="15" t="s">
         <v>10</v>
@@ -5288,9 +5196,8 @@
       <c r="F132" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G132" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B132,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G132" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="133" customFormat="1" spans="1:7">
@@ -5298,10 +5205,10 @@
         <v>7</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D133" s="15" t="s">
         <v>10</v>
@@ -5312,9 +5219,8 @@
       <c r="F133" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G133" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B133,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G133" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="134" customFormat="1" spans="1:7">
@@ -5322,10 +5228,10 @@
         <v>7</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>10</v>
@@ -5336,9 +5242,8 @@
       <c r="F134" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G134" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B134,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G134" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:7">
@@ -5346,23 +5251,22 @@
         <v>7</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="F135" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G135" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B135,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G135" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:7">
@@ -5370,10 +5274,10 @@
         <v>7</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>10</v>
@@ -5385,7 +5289,7 @@
         <v>12</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:7">
@@ -5393,10 +5297,10 @@
         <v>7</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D137" s="15" t="s">
         <v>10</v>
@@ -5408,7 +5312,7 @@
         <v>12</v>
       </c>
       <c r="G137" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" customFormat="1" spans="1:7">
@@ -5416,10 +5320,10 @@
         <v>7</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>10</v>
@@ -5431,7 +5335,7 @@
         <v>12</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" customFormat="1" spans="1:7">
@@ -5439,10 +5343,10 @@
         <v>7</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D139" s="15" t="s">
         <v>10</v>
@@ -5454,7 +5358,7 @@
         <v>12</v>
       </c>
       <c r="G139" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" customFormat="1" spans="1:7">
@@ -5462,10 +5366,10 @@
         <v>7</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>10</v>
@@ -5477,7 +5381,7 @@
         <v>12</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" customFormat="1" spans="1:7">
@@ -5485,10 +5389,10 @@
         <v>7</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D141" s="15" t="s">
         <v>10</v>
@@ -5500,7 +5404,7 @@
         <v>12</v>
       </c>
       <c r="G141" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" customFormat="1" spans="1:7">
@@ -5508,10 +5412,10 @@
         <v>7</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>10</v>
@@ -5523,7 +5427,7 @@
         <v>12</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143" customFormat="1" spans="1:7">
@@ -5531,10 +5435,10 @@
         <v>7</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>10</v>
@@ -5546,7 +5450,7 @@
         <v>12</v>
       </c>
       <c r="G143" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" customFormat="1" spans="1:7">
@@ -5554,10 +5458,10 @@
         <v>7</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>10</v>
@@ -5569,7 +5473,7 @@
         <v>12</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" customFormat="1" spans="1:7">
@@ -5577,10 +5481,10 @@
         <v>7</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D145" s="15" t="s">
         <v>10</v>
@@ -5592,32 +5496,77 @@
         <v>12</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" customFormat="1" spans="1:7">
-      <c r="A146" s="15"/>
-      <c r="B146" s="15"/>
-      <c r="C146" s="15"/>
-      <c r="D146" s="15"/>
-      <c r="E146" s="15"/>
-      <c r="F146" s="17"/>
+      <c r="A146" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B146" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G146" s="19" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="147" customFormat="1" spans="1:7">
-      <c r="A147" s="15"/>
-      <c r="B147" s="15"/>
-      <c r="C147" s="15"/>
-      <c r="D147" s="15"/>
-      <c r="E147" s="15"/>
-      <c r="F147" s="17"/>
+      <c r="A147" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B147" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="D147" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G147" s="19" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="148" customFormat="1" spans="1:7">
-      <c r="A148" s="15"/>
-      <c r="B148" s="15"/>
-      <c r="C148" s="15"/>
-      <c r="D148" s="15"/>
-      <c r="E148" s="15"/>
-      <c r="F148" s="17"/>
+      <c r="A148" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B148" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C148" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D148" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="19" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="149" customFormat="1" spans="1:7">
       <c r="A149" s="15"/>
@@ -5732,31 +5681,85 @@
       <c r="F162" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G144" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G148" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B128">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="0" priority="23">
       <formula>COUNTIF(Sheet2!#REF!,A129)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C128">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C129">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C130">
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C131">
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C132">
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C134">
+    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C135">
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C136">
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C137">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C138">
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C139">
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C140">
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C141">
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C142">
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C143">
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C144">
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C145">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B146">
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C146">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B147">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C147">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C131">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="B148">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C132">
+  <conditionalFormatting sqref="C148">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C127 C133:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  <conditionalFormatting sqref="C1:C127 C133 C149:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5779,297 +5782,297 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" ht="77" customHeight="1" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:5">
       <c r="A14" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -6079,383 +6082,383 @@
         <v>8</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" s="3" customFormat="1" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" s="3" customFormat="1" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="115.2" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="28.8" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:5">
       <c r="A49" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="100.8" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:5">
       <c r="A60" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:5">
       <c r="A61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:5">
       <c r="A62" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="63" s="3" customFormat="1" spans="1:5">
       <c r="A63" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:5">
       <c r="A64" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -6470,266 +6473,304 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A878"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:D877"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="131.333333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.15" spans="1:1">
+    <row r="1" ht="15.15" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="2" ht="15.15" spans="1:1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2" ht="15.15" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" ht="15.15" spans="1:1">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D2" t="str">
+        <f>IF(ISNUMBER(MATCH(B2,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
+      </c>
+    </row>
+    <row r="3" ht="15.15" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" ht="15.15" spans="1:1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" ht="15.15" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" ht="15.15" spans="1:1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" ht="15.15" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" ht="15.15" spans="1:1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" ht="15.15" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" ht="15.15" spans="1:1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" ht="15.15" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" ht="15.15" spans="1:1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" ht="15.15" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="9" ht="15.15" spans="1:1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" ht="15.15" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" ht="15.15" spans="1:1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" ht="15.15" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" ht="15.15" spans="1:1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" ht="15.15" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" ht="15.15" spans="1:1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" ht="15.15" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="13" ht="15.15" spans="1:1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" ht="15.15" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="14" ht="15.15" spans="1:1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" ht="15.15" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" ht="15.15" spans="1:1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" ht="15.15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="16" ht="15.15" spans="1:1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" ht="15.15" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" ht="15.15" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" ht="15.15" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" ht="15.15" spans="1:1">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="20" ht="15.15" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" ht="15.15" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>251</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" ht="15.15" spans="1:1">
       <c r="A22" s="2" t="s">
-        <v>163</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" ht="15.15" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" ht="15.15" spans="1:1">
       <c r="A24" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" ht="15.15" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" ht="15.15" spans="1:1">
       <c r="A26" s="2" t="s">
-        <v>109</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" ht="15.15" spans="1:1">
       <c r="A27" s="2" t="s">
-        <v>203</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" ht="15.15" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>231</v>
+        <v>302</v>
       </c>
     </row>
     <row r="29" ht="15.15" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>229</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" ht="15.15" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>233</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" ht="15.15" spans="1:1">
       <c r="A31" s="2" t="s">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" ht="15.15" spans="1:1">
       <c r="A32" s="2" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" ht="15.15" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" ht="15.15" spans="1:1">
       <c r="A34" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" ht="15.15" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" ht="15.15" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" ht="15.15" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" ht="15.15" spans="1:1">
       <c r="A38" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" ht="15.15" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" ht="15.15" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" ht="15.15" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>191</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" ht="15.15" spans="1:1">
       <c r="A42" s="2" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" ht="15.15" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>77</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" ht="15.15" spans="1:1">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="45" ht="15.15" spans="1:1">
-      <c r="A45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="46" ht="15.15" spans="1:1">
-      <c r="A46" s="2"/>
+      <c r="A46" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="47" ht="15.15" spans="1:1">
-      <c r="A47" s="2"/>
+      <c r="A47" s="2" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="48" ht="15.15" spans="1:1">
-      <c r="A48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="49" ht="15.15" spans="1:1">
-      <c r="A49" s="2"/>
+      <c r="A49" s="2" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="50" ht="15.15" spans="1:1">
-      <c r="A50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="51" ht="15.15" spans="1:1">
-      <c r="A51" s="2"/>
+      <c r="A51" s="2" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="52" ht="15.15" spans="1:1">
-      <c r="A52" s="2"/>
+      <c r="A52" s="2" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="53" ht="15.15" spans="1:1">
-      <c r="A53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="54" ht="15.15" spans="1:1">
-      <c r="A54" s="2"/>
+      <c r="A54" s="2" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="55" ht="15.15" spans="1:1">
-      <c r="A55" s="2"/>
+      <c r="A55" s="2" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="56" ht="15.15" spans="1:1">
-      <c r="A56" s="2"/>
+      <c r="A56" s="2" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="57" ht="15.15" spans="1:1">
-      <c r="A57" s="2"/>
+      <c r="A57" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="58" ht="15.15" spans="1:1">
       <c r="A58" s="2"/>
@@ -9190,9 +9231,6 @@
     </row>
     <row r="877" ht="15.15" spans="1:1">
       <c r="A877" s="2"/>
-    </row>
-    <row r="878" ht="15.15" spans="1:1">
-      <c r="A878" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
